--- a/Wasserstein_plots/wasserstein_metrics.xlsx
+++ b/Wasserstein_plots/wasserstein_metrics.xlsx
@@ -474,17 +474,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-05-28 11:14:33</t>
+          <t>2025-06-02 10:24:21</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.002316</v>
+        <v>0.027164</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003259999999999985</v>
+        <v>0.003812000000000038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002787999999999993</v>
+        <v>0.01548800000000002</v>
       </c>
     </row>
     <row r="3">
@@ -500,17 +500,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-05-28 11:14:41</t>
+          <t>2025-06-02 10:24:27</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.012224</v>
+        <v>0.016752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006668000000000007</v>
+        <v>0.004232000000000014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009446000000000003</v>
+        <v>0.01049200000000001</v>
       </c>
     </row>
     <row r="4">
@@ -526,17 +526,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-05-28 11:14:49</t>
+          <t>2025-06-02 10:24:32</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.009379999999999999</v>
+        <v>0.011812</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006435999999999997</v>
+        <v>0.003187999999999969</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007907999999999998</v>
+        <v>0.007499999999999984</v>
       </c>
     </row>
     <row r="5">
@@ -552,17 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-05-28 11:14:58</t>
+          <t>2025-06-02 10:24:38</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.188232</v>
+        <v>0.297284</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08673200000000003</v>
+        <v>0.05743600000000004</v>
       </c>
       <c r="F5" t="n">
-        <v>0.137482</v>
+        <v>0.17736</v>
       </c>
     </row>
     <row r="6">
@@ -578,17 +578,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-05-28 11:15:06</t>
+          <t>2025-06-02 10:24:44</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.025496</v>
+        <v>0.107788</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01065199999999999</v>
+        <v>0.02088000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.018074</v>
+        <v>0.064334</v>
       </c>
     </row>
     <row r="7">
@@ -604,17 +604,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-05-28 11:15:14</t>
+          <t>2025-06-02 10:24:50</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.011664</v>
+        <v>0.01764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006892000000000009</v>
+        <v>0.004679999999999906</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009278000000000005</v>
+        <v>0.01115999999999995</v>
       </c>
     </row>
     <row r="8">
@@ -630,17 +630,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-05-28 11:15:22</t>
+          <t>2025-06-02 10:24:56</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.009908</v>
+        <v>0.043916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003408000000000022</v>
+        <v>0.008044000000000051</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006658000000000011</v>
+        <v>0.02598000000000002</v>
       </c>
     </row>
     <row r="9">
@@ -656,17 +656,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-05-28 11:15:31</t>
+          <t>2025-06-02 10:25:01</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.007064</v>
+        <v>0.038976</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003176000000000012</v>
+        <v>0.007000000000000006</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005120000000000006</v>
+        <v>0.022988</v>
       </c>
     </row>
     <row r="10">
@@ -682,17 +682,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-05-28 11:15:39</t>
+          <t>2025-06-02 10:25:07</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.190548</v>
+        <v>0.27012</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08999200000000002</v>
+        <v>0.053624</v>
       </c>
       <c r="F10" t="n">
-        <v>0.14027</v>
+        <v>0.161872</v>
       </c>
     </row>
     <row r="11">
@@ -708,17 +708,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-05-28 11:15:48</t>
+          <t>2025-06-02 10:25:13</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.027812</v>
+        <v>0.080624</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01391199999999998</v>
+        <v>0.01706799999999997</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02086199999999999</v>
+        <v>0.04884599999999999</v>
       </c>
     </row>
     <row r="12">
@@ -734,17 +734,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-05-28 11:15:57</t>
+          <t>2025-06-02 10:25:19</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.009348</v>
+        <v>0.044804</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003632000000000024</v>
+        <v>0.008491999999999944</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006490000000000012</v>
+        <v>0.02664799999999997</v>
       </c>
     </row>
     <row r="13">
@@ -760,17 +760,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-05-28 11:16:07</t>
+          <t>2025-06-02 10:25:24</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.002844</v>
+        <v>0.00494</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00023200000000001</v>
+        <v>0.001044000000000045</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001538000000000005</v>
+        <v>0.002992000000000022</v>
       </c>
     </row>
     <row r="14">
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2025-05-28 11:16:18</t>
+          <t>2025-06-02 10:25:30</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.200456</v>
+        <v>0.314036</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09340000000000004</v>
+        <v>0.06166800000000006</v>
       </c>
       <c r="F14" t="n">
-        <v>0.146928</v>
+        <v>0.187852</v>
       </c>
     </row>
     <row r="15">
@@ -812,17 +812,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-05-28 11:16:26</t>
+          <t>2025-06-02 10:25:35</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.03772</v>
+        <v>0.12454</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01732</v>
+        <v>0.02511200000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02752</v>
+        <v>0.07482600000000002</v>
       </c>
     </row>
     <row r="16">
@@ -838,17 +838,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-05-28 11:16:35</t>
+          <t>2025-06-02 10:25:41</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.0005600000000000002</v>
+        <v>0.0008879999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000224000000000002</v>
+        <v>0.0004479999999998929</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003920000000000011</v>
+        <v>0.0006679999999999464</v>
       </c>
     </row>
     <row r="17">
@@ -864,17 +864,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-05-28 11:16:44</t>
+          <t>2025-06-02 10:25:48</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.197612</v>
+        <v>0.309096</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09316800000000003</v>
+        <v>0.06062400000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.14539</v>
+        <v>0.18486</v>
       </c>
     </row>
     <row r="18">
@@ -890,17 +890,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-05-28 11:16:58</t>
+          <t>2025-06-02 10:25:53</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.034876</v>
+        <v>0.1196</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01708799999999999</v>
+        <v>0.02406799999999998</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02598199999999999</v>
+        <v>0.071834</v>
       </c>
     </row>
     <row r="19">
@@ -916,17 +916,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-05-28 11:17:11</t>
+          <t>2025-06-02 10:25:59</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.002284</v>
+        <v>0.005828</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000456000000000012</v>
+        <v>0.001491999999999938</v>
       </c>
       <c r="F19" t="n">
-        <v>0.001370000000000006</v>
+        <v>0.003659999999999969</v>
       </c>
     </row>
     <row r="20">
@@ -942,17 +942,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2025-05-28 11:17:26</t>
+          <t>2025-06-02 10:26:05</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.162736</v>
+        <v>0.189496</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07608000000000004</v>
+        <v>0.03655600000000003</v>
       </c>
       <c r="F20" t="n">
-        <v>0.119408</v>
+        <v>0.113026</v>
       </c>
     </row>
     <row r="21">
@@ -968,17 +968,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-05-28 11:17:40</t>
+          <t>2025-06-02 10:26:11</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.199896</v>
+        <v>0.314924</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09362400000000004</v>
+        <v>0.06211599999999995</v>
       </c>
       <c r="F21" t="n">
-        <v>0.14676</v>
+        <v>0.18852</v>
       </c>
     </row>
     <row r="22">
@@ -994,17 +994,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-05-28 11:17:49</t>
+          <t>2025-06-02 10:26:16</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.03716</v>
+        <v>0.125428</v>
       </c>
       <c r="E22" t="n">
-        <v>0.017544</v>
+        <v>0.02555999999999992</v>
       </c>
       <c r="F22" t="n">
-        <v>0.027352</v>
+        <v>0.07549399999999996</v>
       </c>
     </row>
     <row r="23">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-05-28 11:17:58</t>
+          <t>2025-06-02 10:26:22</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.981196</v>
+        <v>0.940716</v>
       </c>
       <c r="E23" t="n">
-        <v>1.42333288538786</v>
+        <v>1.361860384342479</v>
       </c>
       <c r="F23" t="n">
-        <v>1.20226444269393</v>
+        <v>1.15128819217124</v>
       </c>
     </row>
     <row r="24">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-05-28 11:18:07</t>
+          <t>2025-06-02 10:26:27</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.485668</v>
+        <v>0.485664</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7082946325057785</v>
+        <v>0.7066225596672331</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5969813162528892</v>
+        <v>0.5961432798336166</v>
       </c>
     </row>
     <row r="25">
@@ -1072,17 +1072,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-05-28 11:18:19</t>
+          <t>2025-06-02 10:26:33</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.871092</v>
+        <v>0.790508</v>
       </c>
       <c r="E25" t="n">
-        <v>1.267388739601597</v>
+        <v>1.14458166073345</v>
       </c>
       <c r="F25" t="n">
-        <v>1.069240369800799</v>
+        <v>0.9675448303667251</v>
       </c>
     </row>
     <row r="26">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-05-28 11:18:29</t>
+          <t>2025-06-02 10:26:38</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.5621039999999999</v>
+        <v>0.508772</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8177517182695725</v>
+        <v>0.7406724761711437</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6899278591347862</v>
+        <v>0.6247222380855719</v>
       </c>
     </row>
     <row r="27">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-05-28 11:18:37</t>
+          <t>2025-06-02 10:26:43</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.974584</v>
+        <v>0.9749279999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>1.418797569712382</v>
+        <v>1.420307166169971</v>
       </c>
       <c r="F27" t="n">
-        <v>1.196690784856191</v>
+        <v>1.197617583084985</v>
       </c>
     </row>
     <row r="28">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-05-28 11:18:45</t>
+          <t>2025-06-02 10:26:48</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.982604</v>
+        <v>0.9816239999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>1.426324223277759</v>
+        <v>1.427850228034651</v>
       </c>
       <c r="F28" t="n">
-        <v>1.204464111638879</v>
+        <v>1.204737114017326</v>
       </c>
     </row>
     <row r="29">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-05-28 11:18:52</t>
+          <t>2025-06-02 10:26:53</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.495528</v>
+        <v>0.455052</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7150383752039308</v>
+        <v>0.6552394652911171</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6052831876019654</v>
+        <v>0.5551457326455586</v>
       </c>
     </row>
     <row r="30">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-05-28 11:18:59</t>
+          <t>2025-06-02 10:26:58</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.110104</v>
+        <v>0.150208</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1560059914583944</v>
+        <v>0.2173040379427477</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1330549957291972</v>
+        <v>0.1837560189713739</v>
       </c>
     </row>
     <row r="31">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:06</t>
+          <t>2025-06-02 10:27:03</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.419092</v>
+        <v>0.431944</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6055904282787842</v>
+        <v>0.6211918038669028</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5123412141393922</v>
+        <v>0.5265679019334514</v>
       </c>
     </row>
     <row r="32">
@@ -1254,17 +1254,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:12</t>
+          <t>2025-06-02 10:27:08</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.006612</v>
+        <v>0.034212</v>
       </c>
       <c r="E32" t="n">
-        <v>0.005748112093614582</v>
+        <v>0.05884121290654205</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00618005604680729</v>
+        <v>0.04652660645327102</v>
       </c>
     </row>
     <row r="33">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:19</t>
+          <t>2025-06-02 10:27:13</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.001408</v>
+        <v>0.040908</v>
       </c>
       <c r="E33" t="n">
-        <v>0.006263775147959653</v>
+        <v>0.06604817530716076</v>
       </c>
       <c r="F33" t="n">
-        <v>0.003835887573979827</v>
+        <v>0.05347808765358038</v>
       </c>
     </row>
     <row r="34">
@@ -1306,17 +1306,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:25</t>
+          <t>2025-06-02 10:27:17</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.385424</v>
+        <v>0.304844</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5590970899994481</v>
+        <v>0.4379591029331859</v>
       </c>
       <c r="F34" t="n">
-        <v>0.472260544999724</v>
+        <v>0.3714015514665929</v>
       </c>
     </row>
     <row r="35">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:32</t>
+          <t>2025-06-02 10:27:22</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.076436</v>
+        <v>0.02310799999999996</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1094810887786519</v>
+        <v>0.03420459907534646</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09295854438932594</v>
+        <v>0.02865629953767321</v>
       </c>
     </row>
     <row r="36">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:38</t>
+          <t>2025-06-02 10:27:27</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.488916</v>
+        <v>0.489264</v>
       </c>
       <c r="E36" t="n">
-        <v>0.710503600288344</v>
+        <v>0.7137012386448067</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5997098001441721</v>
+        <v>0.6014826193224033</v>
       </c>
     </row>
     <row r="37">
@@ -1384,17 +1384,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:45</t>
+          <t>2025-06-02 10:27:32</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.496936</v>
+        <v>0.49596</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7180296558151184</v>
+        <v>0.7212294788936287</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6074828279075593</v>
+        <v>0.6085947394468143</v>
       </c>
     </row>
     <row r="38">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:52</t>
+          <t>2025-06-02 10:27:37</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.308988</v>
+        <v>0.281736</v>
       </c>
       <c r="E38" t="n">
-        <v>0.449643699926244</v>
+        <v>0.4039207666942338</v>
       </c>
       <c r="F38" t="n">
-        <v>0.379315849963122</v>
+        <v>0.3428283833471169</v>
       </c>
     </row>
     <row r="39">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025-05-28 11:19:58</t>
+          <t>2025-06-02 10:27:41</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.103492</v>
+        <v>0.18442</v>
       </c>
       <c r="E39" t="n">
-        <v>0.151506516576671</v>
+        <v>0.2757999378440603</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1274992582883355</v>
+        <v>0.2301099689220301</v>
       </c>
     </row>
     <row r="40">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-05-28 11:20:05</t>
+          <t>2025-06-02 10:27:46</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.111512</v>
+        <v>0.191116</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1589629173305408</v>
+        <v>0.2832901900403901</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1352374586652704</v>
+        <v>0.2372030950201951</v>
       </c>
     </row>
     <row r="41">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025-05-28 11:20:12</t>
+          <t>2025-06-02 10:27:51</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.41248</v>
+        <v>0.466156</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6010568563755039</v>
+        <v>0.6796477257508993</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5067684281877519</v>
+        <v>0.5729018628754496</v>
       </c>
     </row>
     <row r="42">
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-05-28 11:20:18</t>
+          <t>2025-06-02 10:27:55</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.4205</v>
+        <v>0.472852</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6085884010108568</v>
+        <v>0.6871870072624107</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5145442005054284</v>
+        <v>0.5800195036312054</v>
       </c>
     </row>
     <row r="43">
@@ -1540,17 +1540,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-05-28 11:20:25</t>
+          <t>2025-06-02 10:28:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.008019999999999999</v>
+        <v>0.006696000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01018965852748891</v>
+        <v>0.009618316550041615</v>
       </c>
       <c r="F43" t="n">
-        <v>0.009104829263744452</v>
+        <v>0.008157158275020808</v>
       </c>
     </row>
   </sheetData>
@@ -1626,24 +1626,24 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.58004</v>
+        <v>0.241604</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008207118861086387</v>
+        <v>0.007804561742980832</v>
       </c>
       <c r="E2" t="n">
-        <v>145010</v>
+        <v>60401</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00827635530789652</v>
+        <v>0.005216336872018681</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0.014668 0.985332]</t>
+          <t>[0.024464 0.975536]</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9838244250358874</v>
+        <v>0.9811995359425153</v>
       </c>
       <c r="I2" t="n">
         <v>0.5</v>
@@ -1661,24 +1661,24 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5832999999999999</v>
+        <v>0.237792</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00541010166263075</v>
+        <v>0.006989015381296567</v>
       </c>
       <c r="E3" t="n">
-        <v>145825</v>
+        <v>59448</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005016355307896521</v>
+        <v>0.009028336872018683</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.012352 0.987648]</t>
+          <t>[0.051628 0.948372]</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9924592351243157</v>
+        <v>0.965317538333734</v>
       </c>
       <c r="I3" t="n">
         <v>0.5</v>
@@ -1696,24 +1696,24 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5867080000000001</v>
+        <v>0.245836</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006747468858764742</v>
+        <v>0.006131060593404699</v>
       </c>
       <c r="E4" t="n">
-        <v>146677</v>
+        <v>61459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001608355307896519</v>
+        <v>0.0009843368720186818</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0.002444 0.997556]</t>
+          <t>[0.007712 0.992288]</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9921532772865368</v>
+        <v>0.982577056143277</v>
       </c>
       <c r="I4" t="n">
         <v>0.5</v>
@@ -1731,24 +1731,24 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.586476</v>
+        <v>0.244792</v>
       </c>
       <c r="D5" t="n">
-        <v>0.006414844035516371</v>
+        <v>0.005679853519237975</v>
       </c>
       <c r="E5" t="n">
-        <v>146619</v>
+        <v>61198</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001840355307896519</v>
+        <v>0.002028336872018681</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[0.005288 0.994712]</t>
+          <t>[0.012652 0.987348]</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.993139141430491</v>
+        <v>0.9850890047446658</v>
       </c>
       <c r="I5" t="n">
         <v>0.5</v>
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.493308</v>
+        <v>0.1841679999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08999808184622603</v>
+        <v>0.06819277803404111</v>
       </c>
       <c r="E6" t="n">
-        <v>123327</v>
+        <v>46042</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09500835530789656</v>
+        <v>0.06265233687201871</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[0.2029 0.7971]</t>
+          <t>[0.321748 0.678252]</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.7911049825504539</v>
+        <v>0.6585356865641112</v>
       </c>
       <c r="I6" t="n">
         <v>0.5</v>
@@ -1801,24 +1801,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.569388</v>
+        <v>0.220724</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007777342476707577</v>
+        <v>0.006538977290066086</v>
       </c>
       <c r="E7" t="n">
-        <v>142347</v>
+        <v>55181</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01892835530789651</v>
+        <v>0.02609633687201867</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0.040164 0.959836]</t>
+          <t>[0.132252 0.867748]</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9753935868393113</v>
+        <v>0.9046256189001768</v>
       </c>
       <c r="I7" t="n">
         <v>0.5</v>
@@ -1836,24 +1836,24 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.586932</v>
+        <v>0.246284</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00757497036297832</v>
+        <v>0.006933061661344145</v>
       </c>
       <c r="E8" t="n">
-        <v>146733</v>
+        <v>61571</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001384355307896519</v>
+        <v>0.0005363368720186811</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[0.003004 0.996996]</t>
+          <t>[0.006824 0.993176]</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9968446307991472</v>
+        <v>1.01434105136084</v>
       </c>
       <c r="I8" t="n">
         <v>0.5</v>
@@ -1871,24 +1871,24 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.015069563325948</v>
+        <v>1.015275413541305</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008640200729547519</v>
+        <v>0.008625384039094981</v>
       </c>
       <c r="E9" t="n">
-        <v>253767.3908314871</v>
+        <v>253818.8533853262</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9849304366740517</v>
+        <v>0.9847245864586952</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[0.985796 0.014204]</t>
+          <t>[0.98608 0.01392]</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.505876699356737</v>
+        <v>0.5064675468328124</v>
       </c>
       <c r="I9" t="n">
         <v>0.5</v>
@@ -1906,24 +1906,24 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.993209250504581</v>
+        <v>1.948302094522683</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02819859279608372</v>
+        <v>0.1945531808300753</v>
       </c>
       <c r="E10" t="n">
-        <v>498302.3126261453</v>
+        <v>487075.5236306708</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006790749495418907</v>
+        <v>0.05169790547731683</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[0.0046 0.9954]</t>
+          <t>[0.045364 0.954636]</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.9937384598363657</v>
+        <v>0.9925037545809665</v>
       </c>
       <c r="I10" t="n">
         <v>0.5</v>
@@ -1941,24 +1941,24 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.503901455770472</v>
+        <v>1.497463135361654</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01861132470761057</v>
+        <v>0.02288760016543078</v>
       </c>
       <c r="E11" t="n">
-        <v>375975.3639426182</v>
+        <v>374365.7838404135</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4960985442295273</v>
+        <v>0.5025368646383459</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[0.500128 0.499872]</t>
+          <t>[0.500416 0.499584]</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.7487317811290686</v>
+        <v>0.7549323925913203</v>
       </c>
       <c r="I11" t="n">
         <v>0.5</v>
@@ -1976,24 +1976,24 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.885016425218226</v>
+        <v>1.798243890390601</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2973948320053307</v>
+        <v>0.3710587177916276</v>
       </c>
       <c r="E12" t="n">
-        <v>471254.1063045565</v>
+        <v>449560.9725976503</v>
       </c>
       <c r="F12" t="n">
-        <v>0.114983574781774</v>
+        <v>0.2017561096093987</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[0.114704 0.885296]</t>
+          <t>[0.195572 0.804428]</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8893342127629691</v>
+        <v>0.9006606427140171</v>
       </c>
       <c r="I12" t="n">
         <v>0.5</v>
@@ -2011,24 +2011,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.574174185539769</v>
+        <v>1.523493526304274</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3647691162949254</v>
+        <v>0.381890251545684</v>
       </c>
       <c r="E13" t="n">
-        <v>393543.5463849423</v>
+        <v>380873.3815760686</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4258258144602312</v>
+        <v>0.4765064736957256</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[0.423692 0.576308]</t>
+          <t>[0.477308 0.522692]</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.754422395334662</v>
+        <v>0.7381464139238284</v>
       </c>
       <c r="I13" t="n">
         <v>0.5</v>
@@ -2046,24 +2046,24 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.991718554461869</v>
+        <v>1.996300758766288</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02478385843679748</v>
+        <v>0.0297054721496181</v>
       </c>
       <c r="E14" t="n">
-        <v>497929.6386154673</v>
+        <v>499075.189691572</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008281445538130981</v>
+        <v>0.003699241233711689</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[0.011212 0.988788]</t>
+          <t>[0.011152 0.988848]</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.9984572034863823</v>
+        <v>1.002222370161301</v>
       </c>
       <c r="I14" t="n">
         <v>0.5</v>
@@ -2081,24 +2081,24 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.992754715258477</v>
+        <v>1.999548287462751</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02745741227350332</v>
+        <v>0.02316676865968031</v>
       </c>
       <c r="E15" t="n">
-        <v>498188.6788146193</v>
+        <v>499887.0718656878</v>
       </c>
       <c r="F15" t="n">
-        <v>0.007245284741522504</v>
+        <v>0.0004517125372489445</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[0.003192 0.996808]</t>
+          <t>[0.004456 0.995544]</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.0021810569554</v>
+        <v>0.9986384294548272</v>
       </c>
       <c r="I15" t="n">
         <v>0.5</v>
